--- a/AutoRappel_Emmaus-Connect-main/test/Rapport inscription bénéficiaire 30 jour-2023-12-06-12-48-08 - Copie.xlsx
+++ b/AutoRappel_Emmaus-Connect-main/test/Rapport inscription bénéficiaire 30 jour-2023-12-06-12-48-08 - Copie.xlsx
@@ -1,66 +1,65 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr date1904="false"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView activeTab="0"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Rapport inscription bénéficiair" r:id="rId3" sheetId="1"/>
+    <sheet name="Rapport inscription bénéficiair" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
 </workbook>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="0" uniqueCount="0"/>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
-      <sz val="11.0"/>
-      <color indexed="8"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color indexed="8"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <sz val="18.0"/>
-      <color rgb="56585B"/>
-      <u val="none"/>
+      <color rgb="0056585B"/>
+      <sz val="18"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <sz val="12.0"/>
-      <color rgb="56585B"/>
-      <u val="none"/>
+      <color rgb="0056585B"/>
+      <sz val="12"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <sz val="12.0"/>
-      <color rgb="56585B"/>
-      <b val="true"/>
-      <u val="none"/>
+      <b val="1"/>
+      <color rgb="0056585B"/>
+      <sz val="12"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <sz val="12.0"/>
-      <color rgb="000000"/>
-      <u val="none"/>
+      <color rgb="00000000"/>
+      <sz val="12"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <sz val="12.0"/>
-      <color rgb="000000"/>
-      <u val="none"/>
+      <color rgb="00000000"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="12"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="7">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="darkGray"/>
@@ -70,26 +69,26 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="F9F9F7"/>
+        <fgColor rgb="00F9F9F7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF"/>
+        <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="E9E8E5"/>
+        <fgColor rgb="00E9E8E5"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="EAF5FC"/>
+        <fgColor rgb="00EAF5FC"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="27">
+  <borders count="30">
     <border>
       <left/>
       <right/>
@@ -102,7 +101,7 @@
     </border>
     <border>
       <right style="thin">
-        <color rgb="8E9297"/>
+        <color rgb="008E9297"/>
       </right>
     </border>
     <border>
@@ -110,7 +109,7 @@
     </border>
     <border>
       <bottom style="thin">
-        <color rgb="D5D3D1"/>
+        <color rgb="00D5D3D1"/>
       </bottom>
     </border>
     <border>
@@ -119,16 +118,16 @@
     </border>
     <border>
       <right style="thin">
-        <color rgb="8E9297"/>
+        <color rgb="008E9297"/>
       </right>
       <bottom style="thin"/>
     </border>
     <border>
       <right style="thin">
-        <color rgb="8E9297"/>
+        <color rgb="008E9297"/>
       </right>
       <bottom style="thin">
-        <color rgb="D5D3D1"/>
+        <color rgb="00D5D3D1"/>
       </bottom>
     </border>
     <border>
@@ -153,44 +152,44 @@
       <left style="thin"/>
       <right style="thin"/>
       <top style="thin">
-        <color rgb="D5D3D1"/>
+        <color rgb="00D5D3D1"/>
       </top>
       <bottom style="thin"/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="D5D3D1"/>
+        <color rgb="00D5D3D1"/>
       </left>
       <right style="thin"/>
       <top style="thin">
-        <color rgb="D5D3D1"/>
+        <color rgb="00D5D3D1"/>
       </top>
       <bottom style="thin"/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="D5D3D1"/>
+        <color rgb="00D5D3D1"/>
       </left>
       <right style="thin">
-        <color rgb="D5D3D1"/>
+        <color rgb="00D5D3D1"/>
       </right>
       <top style="thin">
-        <color rgb="D5D3D1"/>
+        <color rgb="00D5D3D1"/>
       </top>
       <bottom style="thin"/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="D5D3D1"/>
+        <color rgb="00D5D3D1"/>
       </left>
       <right style="thin">
-        <color rgb="D5D3D1"/>
+        <color rgb="00D5D3D1"/>
       </right>
       <top style="thin">
-        <color rgb="D5D3D1"/>
+        <color rgb="00D5D3D1"/>
       </top>
       <bottom style="thin">
-        <color rgb="D5D3D1"/>
+        <color rgb="00D5D3D1"/>
       </bottom>
     </border>
     <border>
@@ -201,28 +200,28 @@
     <border>
       <left style="thin"/>
       <top style="thin">
-        <color rgb="D5D3D1"/>
+        <color rgb="00D5D3D1"/>
       </top>
       <bottom style="thin"/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="D5D3D1"/>
+        <color rgb="00D5D3D1"/>
       </left>
       <top style="thin">
-        <color rgb="D5D3D1"/>
+        <color rgb="00D5D3D1"/>
       </top>
       <bottom style="thin"/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="D5D3D1"/>
+        <color rgb="00D5D3D1"/>
       </left>
       <top style="thin">
-        <color rgb="D5D3D1"/>
+        <color rgb="00D5D3D1"/>
       </top>
       <bottom style="thin">
-        <color rgb="D5D3D1"/>
+        <color rgb="00D5D3D1"/>
       </bottom>
     </border>
     <border>
@@ -237,237 +236,629 @@
     <border>
       <right style="thin"/>
       <top style="thin">
-        <color rgb="D5D3D1"/>
+        <color rgb="00D5D3D1"/>
       </top>
       <bottom style="thin"/>
     </border>
     <border>
       <right style="thin">
-        <color rgb="D5D3D1"/>
+        <color rgb="00D5D3D1"/>
       </right>
       <top style="thin">
-        <color rgb="D5D3D1"/>
+        <color rgb="00D5D3D1"/>
       </top>
       <bottom style="thin"/>
     </border>
     <border>
       <right style="thin">
-        <color rgb="D5D3D1"/>
+        <color rgb="00D5D3D1"/>
       </right>
       <top style="thin">
-        <color rgb="D5D3D1"/>
+        <color rgb="00D5D3D1"/>
       </top>
       <bottom style="thin">
-        <color rgb="D5D3D1"/>
+        <color rgb="00D5D3D1"/>
       </bottom>
     </border>
     <border>
       <bottom style="thin">
-        <color rgb="8E9297"/>
+        <color rgb="008E9297"/>
       </bottom>
     </border>
     <border>
       <right style="thin">
-        <color rgb="8E9297"/>
+        <color rgb="008E9297"/>
       </right>
       <bottom style="thin">
-        <color rgb="8E9297"/>
+        <color rgb="008E9297"/>
       </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D5D3D1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D5D3D1"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D5D3D1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D5D3D1"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D5D3D1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D5D3D1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyBorder="true" applyFill="true"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyBorder="true" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyBorder="true" applyFill="true"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="15" xfId="0" applyBorder="true" applyFill="true" applyFont="true"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="15" xfId="0" applyBorder="true" applyNumberFormat="true" applyFill="true" applyFont="true">
+  <cellXfs count="21">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="19" xfId="0" applyBorder="true" applyFill="true" applyFont="true"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="24" xfId="0" applyBorder="true" applyFill="true" applyFont="true"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="15" xfId="0" applyBorder="true" applyNumberFormat="true" applyFill="true" applyFont="true">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="24" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFill="true" applyFont="true"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyBorder="true" applyFill="true" applyFont="true"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="25" xfId="0" applyBorder="true" applyFill="true" applyFont="true"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="26" xfId="0" applyBorder="true" applyFill="true" applyFont="true"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="25" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="26" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  </cellStyles>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
+</file>
+
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="1F497D"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="EEECE1"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4F81BD"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="C0504D"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="9BBB59"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8064A2"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4BACC6"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="F79646"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000FF"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="800080"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Cambria"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="1"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+</a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Z77"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="4.328125" customWidth="true"/>
-    <col min="2" max="2" width="32.0" customWidth="true"/>
-    <col min="3" max="3" width="8.0" customWidth="true"/>
-    <col min="4" max="4" width="30.0" customWidth="true"/>
-    <col min="5" max="5" width="18.0" customWidth="true"/>
-    <col min="6" max="6" width="30.0" customWidth="true"/>
+    <col width="4.328125" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1"/>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="2"/>
+      <c r="A1" s="1" t="n"/>
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="2" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="1"/>
+      <c r="A2" s="1" t="n"/>
       <c r="B2" s="3" t="inlineStr">
         <is>
           <t>Rapport inscription bénéficiaire 30 jour</t>
         </is>
       </c>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="2"/>
+      <c r="C2" s="3" t="n"/>
+      <c r="D2" s="3" t="n"/>
+      <c r="E2" s="3" t="n"/>
+      <c r="F2" s="2" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="1"/>
+      <c r="A3" s="1" t="n"/>
       <c r="B3" s="4" t="inlineStr">
         <is>
           <t>Au 2023-12-06 12:48:08 Heure d'Europe centrale/CET • Généré par Connect Lyon • Trié par Date de création (Ascendant)</t>
         </is>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="2"/>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="n"/>
+      <c r="F3" s="2" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="5"/>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="6"/>
+      <c r="A4" s="5" t="n"/>
+      <c r="B4" s="5" t="n"/>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="n"/>
+      <c r="F4" s="6" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="7"/>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="8"/>
+      <c r="A5" s="7" t="n"/>
+      <c r="B5" s="7" t="n"/>
+      <c r="C5" s="7" t="n"/>
+      <c r="D5" s="7" t="n"/>
+      <c r="E5" s="7" t="n"/>
+      <c r="F5" s="8" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="7"/>
+      <c r="A6" s="7" t="n"/>
       <c r="B6" s="9" t="inlineStr">
         <is>
           <t>Filtré par</t>
         </is>
       </c>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="8"/>
+      <c r="C6" s="9" t="n"/>
+      <c r="D6" s="9" t="n"/>
+      <c r="E6" s="9" t="n"/>
+      <c r="F6" s="8" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="7"/>
+      <c r="A7" s="7" t="n"/>
       <c r="B7" s="10" t="inlineStr">
         <is>
           <t>Afficher: Mes contacts</t>
         </is>
       </c>
-      <c r="C7" s="10"/>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="8"/>
+      <c r="C7" s="10" t="n"/>
+      <c r="D7" s="10" t="n"/>
+      <c r="E7" s="10" t="n"/>
+      <c r="F7" s="8" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="7"/>
+      <c r="A8" s="7" t="n"/>
       <c r="B8" s="10" t="inlineStr">
         <is>
           <t>Champ de date: Date de création égal à 30 derniers jours (07/11/2023 en 06/12/2023)</t>
         </is>
       </c>
-      <c r="C8" s="10"/>
-      <c r="D8" s="10"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="8"/>
+      <c r="C8" s="10" t="n"/>
+      <c r="D8" s="10" t="n"/>
+      <c r="E8" s="10" t="n"/>
+      <c r="F8" s="8" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="7"/>
+      <c r="A9" s="7" t="n"/>
       <c r="B9" s="10" t="inlineStr">
         <is>
           <t>Fiche créée par: Nom complet différent de Diana Luc</t>
         </is>
       </c>
-      <c r="C9" s="10"/>
-      <c r="D9" s="10"/>
-      <c r="E9" s="10"/>
-      <c r="F9" s="8"/>
+      <c r="C9" s="10" t="n"/>
+      <c r="D9" s="10" t="n"/>
+      <c r="E9" s="10" t="n"/>
+      <c r="F9" s="8" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="7"/>
+      <c r="A10" s="7" t="n"/>
       <c r="B10" s="10" t="inlineStr">
         <is>
           <t>Fiche créée par: Nom complet différent de Céline Rosset</t>
         </is>
       </c>
-      <c r="C10" s="10"/>
-      <c r="D10" s="10"/>
-      <c r="E10" s="10"/>
-      <c r="F10" s="8"/>
+      <c r="C10" s="10" t="n"/>
+      <c r="D10" s="10" t="n"/>
+      <c r="E10" s="10" t="n"/>
+      <c r="F10" s="8" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="7"/>
+      <c r="A11" s="7" t="n"/>
       <c r="B11" s="10" t="inlineStr">
         <is>
           <t>Fiche créée par: Nom complet différent de Cécilia Turuban</t>
         </is>
       </c>
-      <c r="C11" s="10"/>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="8"/>
+      <c r="C11" s="10" t="n"/>
+      <c r="D11" s="10" t="n"/>
+      <c r="E11" s="10" t="n"/>
+      <c r="F11" s="8" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="7"/>
+      <c r="A12" s="7" t="n"/>
       <c r="B12" s="10" t="inlineStr">
         <is>
           <t>Type d'enregistrement du contact égal à Bénéficiaire</t>
         </is>
       </c>
-      <c r="C12" s="10"/>
-      <c r="D12" s="10"/>
-      <c r="E12" s="10"/>
-      <c r="F12" s="8"/>
+      <c r="C12" s="10" t="n"/>
+      <c r="D12" s="10" t="n"/>
+      <c r="E12" s="10" t="n"/>
+      <c r="F12" s="8" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="7"/>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="8"/>
+      <c r="A13" s="7" t="n"/>
+      <c r="B13" s="7" t="n"/>
+      <c r="C13" s="7" t="n"/>
+      <c r="D13" s="7" t="n"/>
+      <c r="E13" s="7" t="n"/>
+      <c r="F13" s="8" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="7"/>
+      <c r="A14" s="7" t="n"/>
       <c r="B14" s="11" t="inlineStr">
         <is>
           <t>Nom complet</t>
         </is>
       </c>
-      <c r="C14" s="11"/>
+      <c r="C14" s="20" t="n"/>
       <c r="D14" s="11" t="inlineStr">
         <is>
           <t>Téléphone mobile</t>
@@ -478,16 +869,16 @@
           <t>Date de création</t>
         </is>
       </c>
-      <c r="F14" s="8"/>
+      <c r="F14" s="8" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="7"/>
+      <c r="A15" s="7" t="n"/>
       <c r="B15" s="12" t="inlineStr">
         <is>
           <t>Thomas RUZIZIYA</t>
         </is>
       </c>
-      <c r="C15" s="12"/>
+      <c r="C15" s="20" t="n"/>
       <c r="D15" s="12" t="inlineStr">
         <is>
           <t>0758306365</t>
@@ -498,16 +889,16 @@
           <t>07/11/2023</t>
         </is>
       </c>
-      <c r="F15" s="8"/>
+      <c r="F15" s="8" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="7"/>
+      <c r="A16" s="7" t="n"/>
       <c r="B16" s="12" t="inlineStr">
         <is>
           <t>Pamela WANYA AKANYI</t>
         </is>
       </c>
-      <c r="C16" s="12"/>
+      <c r="C16" s="20" t="n"/>
       <c r="D16" s="12" t="inlineStr">
         <is>
           <t>0663287355</t>
@@ -518,16 +909,16 @@
           <t>07/11/2023</t>
         </is>
       </c>
-      <c r="F16" s="8"/>
+      <c r="F16" s="8" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="7"/>
+      <c r="A17" s="7" t="n"/>
       <c r="B17" s="12" t="inlineStr">
         <is>
           <t>Mohamed SAID HASSANE</t>
         </is>
       </c>
-      <c r="C17" s="12"/>
+      <c r="C17" s="20" t="n"/>
       <c r="D17" s="12" t="inlineStr">
         <is>
           <t>0650592464</t>
@@ -538,16 +929,16 @@
           <t>07/11/2023</t>
         </is>
       </c>
-      <c r="F17" s="8"/>
+      <c r="F17" s="8" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="7"/>
+      <c r="A18" s="7" t="n"/>
       <c r="B18" s="12" t="inlineStr">
         <is>
           <t>Salah MERDJI</t>
         </is>
       </c>
-      <c r="C18" s="12"/>
+      <c r="C18" s="20" t="n"/>
       <c r="D18" s="12" t="inlineStr">
         <is>
           <t>06 27 72 34 15</t>
@@ -558,16 +949,16 @@
           <t>07/11/2023</t>
         </is>
       </c>
-      <c r="F18" s="8"/>
+      <c r="F18" s="8" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="7"/>
+      <c r="A19" s="7" t="n"/>
       <c r="B19" s="12" t="inlineStr">
         <is>
           <t>Hasna RABI</t>
         </is>
       </c>
-      <c r="C19" s="12"/>
+      <c r="C19" s="20" t="n"/>
       <c r="D19" s="12" t="inlineStr">
         <is>
           <t>0758141942</t>
@@ -578,16 +969,16 @@
           <t>07/11/2023</t>
         </is>
       </c>
-      <c r="F19" s="8"/>
+      <c r="F19" s="8" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="7"/>
+      <c r="A20" s="7" t="n"/>
       <c r="B20" s="12" t="inlineStr">
         <is>
           <t>Joy EDOS</t>
         </is>
       </c>
-      <c r="C20" s="12"/>
+      <c r="C20" s="20" t="n"/>
       <c r="D20" s="12" t="inlineStr">
         <is>
           <t>0753521094</t>
@@ -598,16 +989,16 @@
           <t>07/11/2023</t>
         </is>
       </c>
-      <c r="F20" s="8"/>
+      <c r="F20" s="8" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="7"/>
+      <c r="A21" s="7" t="n"/>
       <c r="B21" s="12" t="inlineStr">
         <is>
           <t>Anas MALHA</t>
         </is>
       </c>
-      <c r="C21" s="12"/>
+      <c r="C21" s="20" t="n"/>
       <c r="D21" s="12" t="inlineStr">
         <is>
           <t>0621664554</t>
@@ -618,16 +1009,16 @@
           <t>09/11/2023</t>
         </is>
       </c>
-      <c r="F21" s="8"/>
+      <c r="F21" s="8" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="7"/>
+      <c r="A22" s="7" t="n"/>
       <c r="B22" s="12" t="inlineStr">
         <is>
           <t>Gomaa Hamadin RAHMATHALLAH</t>
         </is>
       </c>
-      <c r="C22" s="12"/>
+      <c r="C22" s="20" t="n"/>
       <c r="D22" s="12" t="inlineStr">
         <is>
           <t>0758868313</t>
@@ -638,16 +1029,16 @@
           <t>09/11/2023</t>
         </is>
       </c>
-      <c r="F22" s="8"/>
+      <c r="F22" s="8" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="7"/>
+      <c r="A23" s="7" t="n"/>
       <c r="B23" s="12" t="inlineStr">
         <is>
           <t>Chifa MOUSSA</t>
         </is>
       </c>
-      <c r="C23" s="12"/>
+      <c r="C23" s="20" t="n"/>
       <c r="D23" s="12" t="inlineStr">
         <is>
           <t>0758868313</t>
@@ -658,16 +1049,19 @@
           <t>09/11/2023</t>
         </is>
       </c>
-      <c r="F23" s="8"/>
+      <c r="F23" s="8" t="n"/>
+      <c r="Z23" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="7"/>
+      <c r="A24" s="7" t="n"/>
       <c r="B24" s="12" t="inlineStr">
         <is>
           <t>Adama VAKABA</t>
         </is>
       </c>
-      <c r="C24" s="12"/>
+      <c r="C24" s="20" t="n"/>
       <c r="D24" s="12" t="inlineStr">
         <is>
           <t>0780462017</t>
@@ -678,16 +1072,16 @@
           <t>09/11/2023</t>
         </is>
       </c>
-      <c r="F24" s="8"/>
+      <c r="F24" s="8" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="7"/>
+      <c r="A25" s="7" t="n"/>
       <c r="B25" s="12" t="inlineStr">
         <is>
           <t>Jalila AOUICHAOUI</t>
         </is>
       </c>
-      <c r="C25" s="12"/>
+      <c r="C25" s="20" t="n"/>
       <c r="D25" s="12" t="inlineStr">
         <is>
           <t>06 95 39 66 34</t>
@@ -698,16 +1092,16 @@
           <t>09/11/2023</t>
         </is>
       </c>
-      <c r="F25" s="8"/>
+      <c r="F25" s="8" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="7"/>
+      <c r="A26" s="7" t="n"/>
       <c r="B26" s="12" t="inlineStr">
         <is>
           <t>Samia DAASSI</t>
         </is>
       </c>
-      <c r="C26" s="12"/>
+      <c r="C26" s="20" t="n"/>
       <c r="D26" s="12" t="inlineStr">
         <is>
           <t>07 73 82 88 80</t>
@@ -718,16 +1112,16 @@
           <t>09/11/2023</t>
         </is>
       </c>
-      <c r="F26" s="8"/>
+      <c r="F26" s="8" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="7"/>
+      <c r="A27" s="7" t="n"/>
       <c r="B27" s="12" t="inlineStr">
         <is>
           <t>Aicha KOUROUMA</t>
         </is>
       </c>
-      <c r="C27" s="12"/>
+      <c r="C27" s="20" t="n"/>
       <c r="D27" s="12" t="inlineStr">
         <is>
           <t>0651999878</t>
@@ -738,19 +1132,19 @@
           <t>14/11/2023</t>
         </is>
       </c>
-      <c r="F27" s="8"/>
+      <c r="F27" s="8" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="7"/>
+      <c r="A28" s="7" t="n"/>
       <c r="B28" s="12" t="inlineStr">
         <is>
           <t>Mariama MAI MOUSSA</t>
         </is>
       </c>
-      <c r="C28" s="12"/>
+      <c r="C28" s="20" t="n"/>
       <c r="D28" s="12" t="inlineStr">
         <is>
-          <t>pas de numéro pour l'instant</t>
+          <t>01</t>
         </is>
       </c>
       <c r="E28" s="12" t="inlineStr">
@@ -758,16 +1152,21 @@
           <t>14/11/2023</t>
         </is>
       </c>
-      <c r="F28" s="8"/>
+      <c r="F28" s="8" t="n"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>0124</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="7"/>
+      <c r="A29" s="7" t="n"/>
       <c r="B29" s="12" t="inlineStr">
         <is>
           <t>Fatiha LAYEB</t>
         </is>
       </c>
-      <c r="C29" s="12"/>
+      <c r="C29" s="20" t="n"/>
       <c r="D29" s="12" t="inlineStr">
         <is>
           <t>0771806304</t>
@@ -778,36 +1177,32 @@
           <t>14/11/2023</t>
         </is>
       </c>
-      <c r="F29" s="8"/>
+      <c r="F29" s="8" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="7"/>
+      <c r="A30" s="7" t="n"/>
       <c r="B30" s="12" t="inlineStr">
         <is>
           <t>Abdelali BENADDOU-IDRISSI</t>
         </is>
       </c>
-      <c r="C30" s="12"/>
-      <c r="D30" s="12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
+      <c r="C30" s="20" t="n"/>
+      <c r="D30" s="12" t="inlineStr"/>
       <c r="E30" s="12" t="inlineStr">
         <is>
           <t>14/11/2023</t>
         </is>
       </c>
-      <c r="F30" s="8"/>
+      <c r="F30" s="8" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="7"/>
+      <c r="A31" s="7" t="n"/>
       <c r="B31" s="12" t="inlineStr">
         <is>
           <t>Hafida ZRIRAK</t>
         </is>
       </c>
-      <c r="C31" s="12"/>
+      <c r="C31" s="20" t="n"/>
       <c r="D31" s="12" t="inlineStr">
         <is>
           <t>0751587059</t>
@@ -818,16 +1213,16 @@
           <t>14/11/2023</t>
         </is>
       </c>
-      <c r="F31" s="8"/>
+      <c r="F31" s="8" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="7"/>
+      <c r="A32" s="7" t="n"/>
       <c r="B32" s="12" t="inlineStr">
         <is>
           <t>Karim DERGAOUI</t>
         </is>
       </c>
-      <c r="C32" s="12"/>
+      <c r="C32" s="20" t="n"/>
       <c r="D32" s="12" t="inlineStr">
         <is>
           <t>0751587059</t>
@@ -838,16 +1233,16 @@
           <t>14/11/2023</t>
         </is>
       </c>
-      <c r="F32" s="8"/>
+      <c r="F32" s="8" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="7"/>
+      <c r="A33" s="7" t="n"/>
       <c r="B33" s="12" t="inlineStr">
         <is>
           <t>Manal AMRI</t>
         </is>
       </c>
-      <c r="C33" s="12"/>
+      <c r="C33" s="20" t="n"/>
       <c r="D33" s="12" t="inlineStr">
         <is>
           <t>0762746623</t>
@@ -858,16 +1253,16 @@
           <t>14/11/2023</t>
         </is>
       </c>
-      <c r="F33" s="8"/>
+      <c r="F33" s="8" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="7"/>
+      <c r="A34" s="7" t="n"/>
       <c r="B34" s="12" t="inlineStr">
         <is>
           <t>Nathalie DEFRETIERE</t>
         </is>
       </c>
-      <c r="C34" s="12"/>
+      <c r="C34" s="20" t="n"/>
       <c r="D34" s="12" t="inlineStr">
         <is>
           <t>0638224841</t>
@@ -878,16 +1273,16 @@
           <t>14/11/2023</t>
         </is>
       </c>
-      <c r="F34" s="8"/>
+      <c r="F34" s="8" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="7"/>
+      <c r="A35" s="7" t="n"/>
       <c r="B35" s="12" t="inlineStr">
         <is>
           <t>Immaculee MUKANOHERI</t>
         </is>
       </c>
-      <c r="C35" s="12"/>
+      <c r="C35" s="20" t="n"/>
       <c r="D35" s="12" t="inlineStr">
         <is>
           <t>0767398021</t>
@@ -898,16 +1293,16 @@
           <t>16/11/2023</t>
         </is>
       </c>
-      <c r="F35" s="8"/>
+      <c r="F35" s="8" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="7"/>
+      <c r="A36" s="7" t="n"/>
       <c r="B36" s="12" t="inlineStr">
         <is>
           <t>Yousra OURAFIH</t>
         </is>
       </c>
-      <c r="C36" s="12"/>
+      <c r="C36" s="20" t="n"/>
       <c r="D36" s="12" t="inlineStr">
         <is>
           <t>07 58 35 43 84</t>
@@ -918,16 +1313,16 @@
           <t>16/11/2023</t>
         </is>
       </c>
-      <c r="F36" s="8"/>
+      <c r="F36" s="8" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="7"/>
+      <c r="A37" s="7" t="n"/>
       <c r="B37" s="12" t="inlineStr">
         <is>
           <t>Aurela TOLI</t>
         </is>
       </c>
-      <c r="C37" s="12"/>
+      <c r="C37" s="20" t="n"/>
       <c r="D37" s="12" t="inlineStr">
         <is>
           <t>0773554837</t>
@@ -938,16 +1333,16 @@
           <t>16/11/2023</t>
         </is>
       </c>
-      <c r="F37" s="8"/>
+      <c r="F37" s="8" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="7"/>
+      <c r="A38" s="7" t="n"/>
       <c r="B38" s="12" t="inlineStr">
         <is>
           <t>Elham ESMAEIL HAKKI</t>
         </is>
       </c>
-      <c r="C38" s="12"/>
+      <c r="C38" s="20" t="n"/>
       <c r="D38" s="12" t="inlineStr">
         <is>
           <t>0774335865 / 07 74 16 58 17</t>
@@ -958,16 +1353,16 @@
           <t>16/11/2023</t>
         </is>
       </c>
-      <c r="F38" s="8"/>
+      <c r="F38" s="8" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="7"/>
+      <c r="A39" s="7" t="n"/>
       <c r="B39" s="12" t="inlineStr">
         <is>
           <t>Andra ESMAEIL HAKKI</t>
         </is>
       </c>
-      <c r="C39" s="12"/>
+      <c r="C39" s="20" t="n"/>
       <c r="D39" s="12" t="inlineStr">
         <is>
           <t>0774335865</t>
@@ -978,16 +1373,16 @@
           <t>16/11/2023</t>
         </is>
       </c>
-      <c r="F39" s="8"/>
+      <c r="F39" s="8" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="7"/>
+      <c r="A40" s="7" t="n"/>
       <c r="B40" s="12" t="inlineStr">
         <is>
           <t>Tetiana DEMIANOVA</t>
         </is>
       </c>
-      <c r="C40" s="12"/>
+      <c r="C40" s="20" t="n"/>
       <c r="D40" s="12" t="inlineStr">
         <is>
           <t>07 82 68 54 13</t>
@@ -998,16 +1393,16 @@
           <t>17/11/2023</t>
         </is>
       </c>
-      <c r="F40" s="8"/>
+      <c r="F40" s="8" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="7"/>
+      <c r="A41" s="7" t="n"/>
       <c r="B41" s="12" t="inlineStr">
         <is>
           <t>Elina KHUDIGOVA</t>
         </is>
       </c>
-      <c r="C41" s="12"/>
+      <c r="C41" s="20" t="n"/>
       <c r="D41" s="12" t="inlineStr">
         <is>
           <t>0606427575</t>
@@ -1018,16 +1413,16 @@
           <t>21/11/2023</t>
         </is>
       </c>
-      <c r="F41" s="8"/>
+      <c r="F41" s="8" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="7"/>
+      <c r="A42" s="7" t="n"/>
       <c r="B42" s="12" t="inlineStr">
         <is>
           <t>Antipas GHUM</t>
         </is>
       </c>
-      <c r="C42" s="12"/>
+      <c r="C42" s="20" t="n"/>
       <c r="D42" s="12" t="inlineStr">
         <is>
           <t>07 51 58 65 69</t>
@@ -1038,16 +1433,16 @@
           <t>21/11/2023</t>
         </is>
       </c>
-      <c r="F42" s="8"/>
+      <c r="F42" s="8" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="7"/>
+      <c r="A43" s="7" t="n"/>
       <c r="B43" s="12" t="inlineStr">
         <is>
           <t>Jonathan COUTI</t>
         </is>
       </c>
-      <c r="C43" s="12"/>
+      <c r="C43" s="20" t="n"/>
       <c r="D43" s="12" t="inlineStr">
         <is>
           <t>07 63 72 22 07</t>
@@ -1058,56 +1453,48 @@
           <t>21/11/2023</t>
         </is>
       </c>
-      <c r="F43" s="8"/>
+      <c r="F43" s="8" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="7"/>
+      <c r="A44" s="7" t="n"/>
       <c r="B44" s="12" t="inlineStr">
         <is>
           <t>Zam-zam ALI</t>
         </is>
       </c>
-      <c r="C44" s="12"/>
-      <c r="D44" s="12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
+      <c r="C44" s="20" t="n"/>
+      <c r="D44" s="12" t="inlineStr"/>
       <c r="E44" s="12" t="inlineStr">
         <is>
           <t>21/11/2023</t>
         </is>
       </c>
-      <c r="F44" s="8"/>
+      <c r="F44" s="8" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="7"/>
+      <c r="A45" s="7" t="n"/>
       <c r="B45" s="12" t="inlineStr">
         <is>
           <t>Marie-Florence MONDJO</t>
         </is>
       </c>
-      <c r="C45" s="12"/>
-      <c r="D45" s="12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
+      <c r="C45" s="20" t="n"/>
+      <c r="D45" s="12" t="inlineStr"/>
       <c r="E45" s="12" t="inlineStr">
         <is>
           <t>21/11/2023</t>
         </is>
       </c>
-      <c r="F45" s="8"/>
+      <c r="F45" s="8" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="7"/>
+      <c r="A46" s="7" t="n"/>
       <c r="B46" s="12" t="inlineStr">
         <is>
           <t>Manuel RODRIGUES</t>
         </is>
       </c>
-      <c r="C46" s="12"/>
+      <c r="C46" s="20" t="n"/>
       <c r="D46" s="12" t="inlineStr">
         <is>
           <t>0631909846</t>
@@ -1118,16 +1505,16 @@
           <t>23/11/2023</t>
         </is>
       </c>
-      <c r="F46" s="8"/>
+      <c r="F46" s="8" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="7"/>
+      <c r="A47" s="7" t="n"/>
       <c r="B47" s="12" t="inlineStr">
         <is>
           <t>Halima KESSOUS</t>
         </is>
       </c>
-      <c r="C47" s="12"/>
+      <c r="C47" s="20" t="n"/>
       <c r="D47" s="12" t="inlineStr">
         <is>
           <t>0698856462</t>
@@ -1138,16 +1525,16 @@
           <t>23/11/2023</t>
         </is>
       </c>
-      <c r="F47" s="8"/>
+      <c r="F47" s="8" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="7"/>
+      <c r="A48" s="7" t="n"/>
       <c r="B48" s="12" t="inlineStr">
         <is>
           <t>Louiza BELBAY</t>
         </is>
       </c>
-      <c r="C48" s="12"/>
+      <c r="C48" s="20" t="n"/>
       <c r="D48" s="12" t="inlineStr">
         <is>
           <t>06 51 64 50 04</t>
@@ -1158,16 +1545,16 @@
           <t>23/11/2023</t>
         </is>
       </c>
-      <c r="F48" s="8"/>
+      <c r="F48" s="8" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="7"/>
+      <c r="A49" s="7" t="n"/>
       <c r="B49" s="12" t="inlineStr">
         <is>
           <t>Louiza BELBEY</t>
         </is>
       </c>
-      <c r="C49" s="12"/>
+      <c r="C49" s="20" t="n"/>
       <c r="D49" s="12" t="inlineStr">
         <is>
           <t>0651655004</t>
@@ -1178,16 +1565,16 @@
           <t>23/11/2023</t>
         </is>
       </c>
-      <c r="F49" s="8"/>
+      <c r="F49" s="8" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="7"/>
+      <c r="A50" s="7" t="n"/>
       <c r="B50" s="12" t="inlineStr">
         <is>
           <t>Koopo GUILAVOGUI</t>
         </is>
       </c>
-      <c r="C50" s="12"/>
+      <c r="C50" s="20" t="n"/>
       <c r="D50" s="12" t="inlineStr">
         <is>
           <t>07 58 69 38 03</t>
@@ -1198,16 +1585,16 @@
           <t>23/11/2023</t>
         </is>
       </c>
-      <c r="F50" s="8"/>
+      <c r="F50" s="8" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="7"/>
+      <c r="A51" s="7" t="n"/>
       <c r="B51" s="12" t="inlineStr">
         <is>
           <t>Pascale THIOLLIER</t>
         </is>
       </c>
-      <c r="C51" s="12"/>
+      <c r="C51" s="20" t="n"/>
       <c r="D51" s="12" t="inlineStr">
         <is>
           <t>06 62 79 10 05</t>
@@ -1218,16 +1605,16 @@
           <t>23/11/2023</t>
         </is>
       </c>
-      <c r="F51" s="8"/>
+      <c r="F51" s="8" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="7"/>
+      <c r="A52" s="7" t="n"/>
       <c r="B52" s="12" t="inlineStr">
         <is>
           <t>Djahid SAADIA</t>
         </is>
       </c>
-      <c r="C52" s="12"/>
+      <c r="C52" s="20" t="n"/>
       <c r="D52" s="12" t="inlineStr">
         <is>
           <t>06 68 45 12 23</t>
@@ -1238,16 +1625,16 @@
           <t>23/11/2023</t>
         </is>
       </c>
-      <c r="F52" s="8"/>
+      <c r="F52" s="8" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="7"/>
+      <c r="A53" s="7" t="n"/>
       <c r="B53" s="12" t="inlineStr">
         <is>
           <t>Ismaël DIATTA</t>
         </is>
       </c>
-      <c r="C53" s="12"/>
+      <c r="C53" s="20" t="n"/>
       <c r="D53" s="12" t="inlineStr">
         <is>
           <t>Pas de numéro</t>
@@ -1258,16 +1645,16 @@
           <t>28/11/2023</t>
         </is>
       </c>
-      <c r="F53" s="8"/>
+      <c r="F53" s="8" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" s="7"/>
+      <c r="A54" s="7" t="n"/>
       <c r="B54" s="12" t="inlineStr">
         <is>
           <t>Sébastien JACQUES GUIOT</t>
         </is>
       </c>
-      <c r="C54" s="12"/>
+      <c r="C54" s="20" t="n"/>
       <c r="D54" s="12" t="inlineStr">
         <is>
           <t>0640882441</t>
@@ -1278,16 +1665,16 @@
           <t>28/11/2023</t>
         </is>
       </c>
-      <c r="F54" s="8"/>
+      <c r="F54" s="8" t="n"/>
     </row>
     <row r="55">
-      <c r="A55" s="7"/>
+      <c r="A55" s="7" t="n"/>
       <c r="B55" s="12" t="inlineStr">
         <is>
           <t>Yassine JEBARI</t>
         </is>
       </c>
-      <c r="C55" s="12"/>
+      <c r="C55" s="20" t="n"/>
       <c r="D55" s="12" t="inlineStr">
         <is>
           <t>0618595718</t>
@@ -1298,16 +1685,16 @@
           <t>28/11/2023</t>
         </is>
       </c>
-      <c r="F55" s="8"/>
+      <c r="F55" s="8" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" s="7"/>
+      <c r="A56" s="7" t="n"/>
       <c r="B56" s="12" t="inlineStr">
         <is>
           <t>Kina KINAVUIDI MAKENGO</t>
         </is>
       </c>
-      <c r="C56" s="12"/>
+      <c r="C56" s="20" t="n"/>
       <c r="D56" s="12" t="inlineStr">
         <is>
           <t>0758561421</t>
@@ -1318,16 +1705,16 @@
           <t>28/11/2023</t>
         </is>
       </c>
-      <c r="F56" s="8"/>
+      <c r="F56" s="8" t="n"/>
     </row>
     <row r="57">
-      <c r="A57" s="7"/>
+      <c r="A57" s="7" t="n"/>
       <c r="B57" s="12" t="inlineStr">
         <is>
           <t>MICKAEL LOUET</t>
         </is>
       </c>
-      <c r="C57" s="12"/>
+      <c r="C57" s="20" t="n"/>
       <c r="D57" s="12" t="inlineStr">
         <is>
           <t>06 26 68 77 37</t>
@@ -1338,16 +1725,16 @@
           <t>28/11/2023</t>
         </is>
       </c>
-      <c r="F57" s="8"/>
+      <c r="F57" s="8" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="7"/>
+      <c r="A58" s="7" t="n"/>
       <c r="B58" s="12" t="inlineStr">
         <is>
           <t>Ovidio CUBA</t>
         </is>
       </c>
-      <c r="C58" s="12"/>
+      <c r="C58" s="20" t="n"/>
       <c r="D58" s="12" t="inlineStr">
         <is>
           <t>0632540488</t>
@@ -1358,16 +1745,16 @@
           <t>28/11/2023</t>
         </is>
       </c>
-      <c r="F58" s="8"/>
+      <c r="F58" s="8" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="7"/>
+      <c r="A59" s="7" t="n"/>
       <c r="B59" s="12" t="inlineStr">
         <is>
           <t>MARIE VAIRAT</t>
         </is>
       </c>
-      <c r="C59" s="12"/>
+      <c r="C59" s="20" t="n"/>
       <c r="D59" s="12" t="inlineStr">
         <is>
           <t>0652621206</t>
@@ -1378,36 +1765,32 @@
           <t>30/11/2023</t>
         </is>
       </c>
-      <c r="F59" s="8"/>
+      <c r="F59" s="8" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="7"/>
+      <c r="A60" s="7" t="n"/>
       <c r="B60" s="12" t="inlineStr">
         <is>
           <t>CYRILLE MBEMBA</t>
         </is>
       </c>
-      <c r="C60" s="12"/>
-      <c r="D60" s="12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
+      <c r="C60" s="20" t="n"/>
+      <c r="D60" s="12" t="inlineStr"/>
       <c r="E60" s="12" t="inlineStr">
         <is>
           <t>30/11/2023</t>
         </is>
       </c>
-      <c r="F60" s="8"/>
+      <c r="F60" s="8" t="n"/>
     </row>
     <row r="61">
-      <c r="A61" s="7"/>
+      <c r="A61" s="7" t="n"/>
       <c r="B61" s="12" t="inlineStr">
         <is>
           <t>Rachel AGRI BWANGA</t>
         </is>
       </c>
-      <c r="C61" s="12"/>
+      <c r="C61" s="20" t="n"/>
       <c r="D61" s="12" t="inlineStr">
         <is>
           <t>07 51 36 34 98</t>
@@ -1418,16 +1801,16 @@
           <t>30/11/2023</t>
         </is>
       </c>
-      <c r="F61" s="8"/>
+      <c r="F61" s="8" t="n"/>
     </row>
     <row r="62">
-      <c r="A62" s="7"/>
+      <c r="A62" s="7" t="n"/>
       <c r="B62" s="12" t="inlineStr">
         <is>
           <t>Stephen OSIFO</t>
         </is>
       </c>
-      <c r="C62" s="12"/>
+      <c r="C62" s="20" t="n"/>
       <c r="D62" s="12" t="inlineStr">
         <is>
           <t>07 58 03 47 00</t>
@@ -1438,36 +1821,32 @@
           <t>30/11/2023</t>
         </is>
       </c>
-      <c r="F62" s="8"/>
+      <c r="F62" s="8" t="n"/>
     </row>
     <row r="63">
-      <c r="A63" s="7"/>
+      <c r="A63" s="7" t="n"/>
       <c r="B63" s="12" t="inlineStr">
         <is>
           <t>Théo DUCHATEAU</t>
         </is>
       </c>
-      <c r="C63" s="12"/>
-      <c r="D63" s="12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
+      <c r="C63" s="20" t="n"/>
+      <c r="D63" s="12" t="inlineStr"/>
       <c r="E63" s="12" t="inlineStr">
         <is>
           <t>01/12/2023</t>
         </is>
       </c>
-      <c r="F63" s="8"/>
+      <c r="F63" s="8" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="7"/>
+      <c r="A64" s="7" t="n"/>
       <c r="B64" s="12" t="inlineStr">
         <is>
           <t>Mountesera, Ibtissem RACHED</t>
         </is>
       </c>
-      <c r="C64" s="12"/>
+      <c r="C64" s="20" t="n"/>
       <c r="D64" s="12" t="inlineStr">
         <is>
           <t>0784607964</t>
@@ -1478,36 +1857,32 @@
           <t>05/12/2023</t>
         </is>
       </c>
-      <c r="F64" s="8"/>
+      <c r="F64" s="8" t="n"/>
     </row>
     <row r="65">
-      <c r="A65" s="7"/>
+      <c r="A65" s="7" t="n"/>
       <c r="B65" s="12" t="inlineStr">
         <is>
           <t>Daouedi MOHAMED (PACK MARAUDE)</t>
         </is>
       </c>
-      <c r="C65" s="12"/>
-      <c r="D65" s="12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
+      <c r="C65" s="20" t="n"/>
+      <c r="D65" s="12" t="inlineStr"/>
       <c r="E65" s="12" t="inlineStr">
         <is>
           <t>05/12/2023</t>
         </is>
       </c>
-      <c r="F65" s="8"/>
+      <c r="F65" s="8" t="n"/>
     </row>
     <row r="66">
-      <c r="A66" s="7"/>
+      <c r="A66" s="7" t="n"/>
       <c r="B66" s="12" t="inlineStr">
         <is>
           <t>Thierno DIALLO</t>
         </is>
       </c>
-      <c r="C66" s="12"/>
+      <c r="C66" s="20" t="n"/>
       <c r="D66" s="12" t="inlineStr">
         <is>
           <t>0780178465</t>
@@ -1518,16 +1893,16 @@
           <t>05/12/2023</t>
         </is>
       </c>
-      <c r="F66" s="8"/>
+      <c r="F66" s="8" t="n"/>
     </row>
     <row r="67">
-      <c r="A67" s="7"/>
+      <c r="A67" s="7" t="n"/>
       <c r="B67" s="12" t="inlineStr">
         <is>
           <t>Djamila RANBI</t>
         </is>
       </c>
-      <c r="C67" s="12"/>
+      <c r="C67" s="20" t="n"/>
       <c r="D67" s="12" t="inlineStr">
         <is>
           <t>0766673297</t>
@@ -1538,16 +1913,16 @@
           <t>05/12/2023</t>
         </is>
       </c>
-      <c r="F67" s="8"/>
+      <c r="F67" s="8" t="n"/>
     </row>
     <row r="68">
-      <c r="A68" s="7"/>
+      <c r="A68" s="7" t="n"/>
       <c r="B68" s="12" t="inlineStr">
         <is>
           <t>Rusalin CUIRAR (PACK MARAUDE)</t>
         </is>
       </c>
-      <c r="C68" s="12"/>
+      <c r="C68" s="20" t="n"/>
       <c r="D68" s="12" t="inlineStr">
         <is>
           <t>0780640049</t>
@@ -1558,16 +1933,16 @@
           <t>05/12/2023</t>
         </is>
       </c>
-      <c r="F68" s="8"/>
+      <c r="F68" s="8" t="n"/>
     </row>
     <row r="69">
-      <c r="A69" s="7"/>
+      <c r="A69" s="7" t="n"/>
       <c r="B69" s="12" t="inlineStr">
         <is>
           <t>Djemaia BRAHIM</t>
         </is>
       </c>
-      <c r="C69" s="12"/>
+      <c r="C69" s="20" t="n"/>
       <c r="D69" s="12" t="inlineStr">
         <is>
           <t>0629244361</t>
@@ -1578,16 +1953,16 @@
           <t>05/12/2023</t>
         </is>
       </c>
-      <c r="F69" s="8"/>
+      <c r="F69" s="8" t="n"/>
     </row>
     <row r="70">
-      <c r="A70" s="7"/>
+      <c r="A70" s="7" t="n"/>
       <c r="B70" s="12" t="inlineStr">
         <is>
           <t>Kristjano GJOKA</t>
         </is>
       </c>
-      <c r="C70" s="12"/>
+      <c r="C70" s="20" t="n"/>
       <c r="D70" s="12" t="inlineStr">
         <is>
           <t>0605574335</t>
@@ -1598,16 +1973,16 @@
           <t>05/12/2023</t>
         </is>
       </c>
-      <c r="F70" s="8"/>
+      <c r="F70" s="8" t="n"/>
     </row>
     <row r="71">
-      <c r="A71" s="7"/>
+      <c r="A71" s="7" t="n"/>
       <c r="B71" s="12" t="inlineStr">
         <is>
           <t>Cheick Hamad DIABY</t>
         </is>
       </c>
-      <c r="C71" s="12"/>
+      <c r="C71" s="20" t="n"/>
       <c r="D71" s="12" t="inlineStr">
         <is>
           <t>0751280901</t>
@@ -1618,16 +1993,16 @@
           <t>05/12/2023</t>
         </is>
       </c>
-      <c r="F71" s="8"/>
+      <c r="F71" s="8" t="n"/>
     </row>
     <row r="72">
-      <c r="A72" s="7"/>
+      <c r="A72" s="7" t="n"/>
       <c r="B72" s="12" t="inlineStr">
         <is>
           <t>Karima BENHAMED</t>
         </is>
       </c>
-      <c r="C72" s="12"/>
+      <c r="C72" s="20" t="n"/>
       <c r="D72" s="12" t="inlineStr">
         <is>
           <t>0662683706</t>
@@ -1638,10 +2013,10 @@
           <t>05/12/2023</t>
         </is>
       </c>
-      <c r="F72" s="8"/>
+      <c r="F72" s="8" t="n"/>
     </row>
     <row r="73">
-      <c r="A73" s="7"/>
+      <c r="A73" s="7" t="n"/>
       <c r="B73" s="13" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1653,113 +2028,113 @@
         </is>
       </c>
       <c r="D73" s="15" t="n">
-        <v>58.0</v>
-      </c>
-      <c r="E73" s="15"/>
-      <c r="F73" s="8"/>
+        <v>58</v>
+      </c>
+      <c r="E73" s="15" t="n"/>
+      <c r="F73" s="8" t="n"/>
     </row>
     <row r="74">
-      <c r="A74" s="16"/>
-      <c r="B74" s="16"/>
-      <c r="C74" s="16"/>
-      <c r="D74" s="16"/>
-      <c r="E74" s="16"/>
-      <c r="F74" s="17"/>
+      <c r="A74" s="16" t="n"/>
+      <c r="B74" s="16" t="n"/>
+      <c r="C74" s="16" t="n"/>
+      <c r="D74" s="16" t="n"/>
+      <c r="E74" s="16" t="n"/>
+      <c r="F74" s="17" t="n"/>
     </row>
     <row r="75">
-      <c r="A75" s="16"/>
-      <c r="B75" s="16"/>
-      <c r="C75" s="16"/>
-      <c r="D75" s="16"/>
-      <c r="E75" s="16"/>
-      <c r="F75" s="17"/>
+      <c r="A75" s="16" t="n"/>
+      <c r="B75" s="16" t="n"/>
+      <c r="C75" s="16" t="n"/>
+      <c r="D75" s="16" t="n"/>
+      <c r="E75" s="16" t="n"/>
+      <c r="F75" s="17" t="n"/>
     </row>
     <row r="76">
-      <c r="A76" s="16"/>
+      <c r="A76" s="16" t="n"/>
       <c r="B76" s="16" t="inlineStr">
         <is>
           <t>Informations confidentielles - Ne pas distribuer</t>
         </is>
       </c>
-      <c r="C76" s="16"/>
-      <c r="D76" s="16"/>
-      <c r="E76" s="16"/>
-      <c r="F76" s="17"/>
+      <c r="C76" s="16" t="n"/>
+      <c r="D76" s="16" t="n"/>
+      <c r="E76" s="16" t="n"/>
+      <c r="F76" s="17" t="n"/>
     </row>
     <row r="77">
-      <c r="A77" s="18"/>
+      <c r="A77" s="18" t="n"/>
       <c r="B77" s="18" t="inlineStr">
         <is>
           <t>Copyright © 2000-2023 salesforce.com, inc. Tous droits réservés.</t>
         </is>
       </c>
-      <c r="C77" s="18"/>
-      <c r="D77" s="18"/>
-      <c r="E77" s="18"/>
-      <c r="F77" s="19"/>
+      <c r="C77" s="18" t="n"/>
+      <c r="D77" s="18" t="n"/>
+      <c r="E77" s="18" t="n"/>
+      <c r="F77" s="19" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="59">
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B61:C61"/>
     <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B64:C64"/>
     <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="B51:C51"/>
     <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="B63:C63"/>
     <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B41:C41"/>
     <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="B72:C72"/>
   </mergeCells>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>